--- a/crdo/dist/20261026_Credo模型_v0.2.2.xlsx
+++ b/crdo/dist/20261026_Credo模型_v0.2.2.xlsx
@@ -7435,26 +7435,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7672,26 +7672,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7793,26 +7793,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7914,26 +7914,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8035,26 +8035,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8156,26 +8156,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -39551,7 +39551,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>33</v>
@@ -42977,7 +42977,7 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">PL!E75/(w8*itc_26+(1-w8)*itc_27)</f>
-        <v>0.00236806227571063</v>
+        <v>0.00236806227571064</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">PL!F75/(w8*itc_27+(1-w8)*itc_28)</f>
